--- a/data/trans_dic/IP11A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11A_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,37 +654,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>25,93%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 56,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 78,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 76,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,02</t>
+          <t>0,0; 45,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,1</t>
+          <t>0,0; 32,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,24</t>
+          <t>0,0; 52,55</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32,75%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>13,48%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 46,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 80,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,39</t>
+          <t>0,0; 28,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,44</t>
+          <t>0,0; 29,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,97</t>
+          <t>0,0; 55,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1012,29 +1012,29 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,18</t>
+          <t>0,0; 75,62</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>33,98%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1282,29 +1282,29 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,46</t>
+          <t>0,0; 68,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1359,27 +1359,27 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>18,06%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1427,29 +1427,29 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 77,62</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,91</t>
+          <t>0,0; 35,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1499,27 +1499,27 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>28,98%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,29 +1567,29 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0,0; 68,76</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 80,17</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 23,17</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 70,67</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,73</t>
+          <t>0,0; 15,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,42</t>
+          <t>0,0; 54,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,14</t>
+          <t>0,0; 27,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,08</t>
+          <t>0,0; 28,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,04; 10,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,85; 9,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>0,0; 24,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,72</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,22</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,23</t>
+          <t>0,6; 5,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,65</t>
+          <t>0,57; 6,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,58</t>
+          <t>2,23; 13,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,49; 17,59</t>
+          <t>2,51; 16,81</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2078,37 +2078,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2146,49 +2146,49 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>617</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>689</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2214,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2380</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2428</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1872</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2275</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3000</t>
+          <t>0; 2597</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2999</t>
+          <t>0; 2788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3769</t>
+          <t>0; 3142</t>
         </is>
       </c>
     </row>
@@ -2286,37 +2286,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2354,49 +2354,49 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1880</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>722</t>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1557</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3433</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3815</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2887</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4143</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6830</t>
+          <t>0; 5708</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3579</t>
+          <t>0; 3564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4729</t>
+          <t>0; 4364</t>
         </is>
       </c>
     </row>
@@ -2504,27 +2504,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1760</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 2591</t>
         </is>
       </c>
     </row>
@@ -2910,27 +2910,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3046,29 +3046,29 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0; 2089</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2903</t>
+          <t>0; 2775</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3123,27 +3123,27 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3191,27 +3191,27 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>640</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3259,29 +3259,29 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>0; 2752</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3323</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3399,27 +3399,27 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3467,29 +3467,29 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>0; 2692</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>0; 2135</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0; 2707</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0; 2767</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 2882</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 3646</t>
+          <t>0; 3611</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3481</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2483</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3527</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2525</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3640</t>
+          <t>0; 3691</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 2940</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3737,37 +3737,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3805,49 +3805,49 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>3230</t>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>485; 4975</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4234</t>
+          <t>626; 7305</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>765; 6280</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 5363</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>481; 4861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>632; 7867</t>
+          <t>0; 3544</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>778; 6218</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 5821</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>485; 5099</t>
+          <t>488; 4903</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>712; 8323</t>
+          <t>713; 8145</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1426; 7423</t>
+          <t>1428; 8407</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1024; 7244</t>
+          <t>990; 6628</t>
         </is>
       </c>
     </row>
